--- a/import-specification/devices/meter.xlsx
+++ b/import-specification/devices/meter.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="129">
   <si>
     <t>Field Type</t>
   </si>
@@ -134,12 +134,18 @@
     <t>datapoints</t>
   </si>
   <si>
+    <t>M_AC_EQ_CAP</t>
+  </si>
+  <si>
+    <t>kvarh</t>
+  </si>
+  <si>
+    <t>Total Reactive Energy capacitive (Sum of Export and Import)</t>
+  </si>
+  <si>
     <t>M_AC_EQ_CAP_EXP</t>
   </si>
   <si>
-    <t>kvarh</t>
-  </si>
-  <si>
     <t>kvar-hours, Negative - Reactive Energy capacitive exported</t>
   </si>
   <si>
@@ -149,6 +155,12 @@
     <t>kvar-hours, Positive - Reactive Energy capacitive imported</t>
   </si>
   <si>
+    <t>M_AC_EQ_IND</t>
+  </si>
+  <si>
+    <t>Total Reactive Energy inductive (Sum of Export and Import)</t>
+  </si>
+  <si>
     <t>M_AC_EQ_IND_EXP</t>
   </si>
   <si>
@@ -230,7 +242,7 @@
     <t>M_AC_OT_TOTAL</t>
   </si>
   <si>
-    <t>hour</t>
+    <t>h</t>
   </si>
   <si>
     <t>Operation Time TOTAL</t>
@@ -741,13 +753,13 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:H47"/>
+  <dimension ref="A1:H49"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="16.425" bestFit="true" customWidth="true" style="0"/>
     <col min="2" max="2" width="24.708" bestFit="true" customWidth="true" style="0"/>
     <col min="3" max="3" width="8.141" bestFit="true" customWidth="true" style="0"/>
-    <col min="4" max="4" width="69.554" bestFit="true" customWidth="true" style="0"/>
+    <col min="4" max="4" width="70.697" bestFit="true" customWidth="true" style="0"/>
     <col min="5" max="5" width="9.283" bestFit="true" customWidth="true" style="0"/>
     <col min="6" max="6" width="12.854" bestFit="true" customWidth="true" style="0"/>
     <col min="7" max="7" width="34.135" bestFit="true" customWidth="true" style="0"/>
@@ -1023,10 +1035,10 @@
         <v>50</v>
       </c>
       <c r="C16" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" t="s">
         <v>51</v>
-      </c>
-      <c r="D16" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="17" spans="1:8">
@@ -1034,13 +1046,13 @@
         <v>38</v>
       </c>
       <c r="B17" t="s">
+        <v>52</v>
+      </c>
+      <c r="C17" t="s">
+        <v>40</v>
+      </c>
+      <c r="D17" t="s">
         <v>53</v>
-      </c>
-      <c r="C17" t="s">
-        <v>51</v>
-      </c>
-      <c r="D17" t="s">
-        <v>54</v>
       </c>
     </row>
     <row r="18" spans="1:8">
@@ -1048,13 +1060,13 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
+        <v>54</v>
+      </c>
+      <c r="C18" t="s">
         <v>55</v>
       </c>
-      <c r="C18" t="s">
+      <c r="D18" t="s">
         <v>56</v>
-      </c>
-      <c r="D18" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="19" spans="1:8">
@@ -1062,13 +1074,13 @@
         <v>38</v>
       </c>
       <c r="B19" t="s">
+        <v>57</v>
+      </c>
+      <c r="C19" t="s">
+        <v>55</v>
+      </c>
+      <c r="D19" t="s">
         <v>58</v>
-      </c>
-      <c r="C19" t="s">
-        <v>56</v>
-      </c>
-      <c r="D19" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:8">
@@ -1076,13 +1088,13 @@
         <v>38</v>
       </c>
       <c r="B20" t="s">
+        <v>59</v>
+      </c>
+      <c r="C20" t="s">
         <v>60</v>
       </c>
-      <c r="C20" t="s">
+      <c r="D20" t="s">
         <v>61</v>
-      </c>
-      <c r="D20" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="21" spans="1:8">
@@ -1090,13 +1102,13 @@
         <v>38</v>
       </c>
       <c r="B21" t="s">
+        <v>62</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
         <v>63</v>
-      </c>
-      <c r="C21" t="s">
-        <v>64</v>
-      </c>
-      <c r="D21" t="s">
-        <v>65</v>
       </c>
     </row>
     <row r="22" spans="1:8">
@@ -1104,13 +1116,13 @@
         <v>38</v>
       </c>
       <c r="B22" t="s">
+        <v>64</v>
+      </c>
+      <c r="C22" t="s">
+        <v>65</v>
+      </c>
+      <c r="D22" t="s">
         <v>66</v>
-      </c>
-      <c r="C22" t="s">
-        <v>64</v>
-      </c>
-      <c r="D22" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="23" spans="1:8">
@@ -1118,6 +1130,9 @@
         <v>38</v>
       </c>
       <c r="B23" t="s">
+        <v>67</v>
+      </c>
+      <c r="C23" t="s">
         <v>68</v>
       </c>
       <c r="D23" t="s">
@@ -1132,10 +1147,10 @@
         <v>70</v>
       </c>
       <c r="C24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" t="s">
         <v>71</v>
-      </c>
-      <c r="D24" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="25" spans="1:8">
@@ -1143,13 +1158,10 @@
         <v>38</v>
       </c>
       <c r="B25" t="s">
+        <v>72</v>
+      </c>
+      <c r="D25" t="s">
         <v>73</v>
-      </c>
-      <c r="C25" t="s">
-        <v>74</v>
-      </c>
-      <c r="D25" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="26" spans="1:8">
@@ -1157,13 +1169,13 @@
         <v>38</v>
       </c>
       <c r="B26" t="s">
+        <v>74</v>
+      </c>
+      <c r="C26" t="s">
+        <v>75</v>
+      </c>
+      <c r="D26" t="s">
         <v>76</v>
-      </c>
-      <c r="C26" t="s">
-        <v>77</v>
-      </c>
-      <c r="D26" t="s">
-        <v>78</v>
       </c>
     </row>
     <row r="27" spans="1:8">
@@ -1171,13 +1183,13 @@
         <v>38</v>
       </c>
       <c r="B27" t="s">
+        <v>77</v>
+      </c>
+      <c r="C27" t="s">
+        <v>78</v>
+      </c>
+      <c r="D27" t="s">
         <v>79</v>
-      </c>
-      <c r="C27" t="s">
-        <v>80</v>
-      </c>
-      <c r="D27" t="s">
-        <v>81</v>
       </c>
     </row>
     <row r="28" spans="1:8">
@@ -1185,13 +1197,13 @@
         <v>38</v>
       </c>
       <c r="B28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C28" t="s">
+        <v>81</v>
+      </c>
+      <c r="D28" t="s">
         <v>82</v>
-      </c>
-      <c r="C28" t="s">
-        <v>83</v>
-      </c>
-      <c r="D28" t="s">
-        <v>84</v>
       </c>
     </row>
     <row r="29" spans="1:8">
@@ -1199,13 +1211,13 @@
         <v>38</v>
       </c>
       <c r="B29" t="s">
+        <v>83</v>
+      </c>
+      <c r="C29" t="s">
+        <v>84</v>
+      </c>
+      <c r="D29" t="s">
         <v>85</v>
-      </c>
-      <c r="C29" t="s">
-        <v>86</v>
-      </c>
-      <c r="D29" t="s">
-        <v>87</v>
       </c>
     </row>
     <row r="30" spans="1:8">
@@ -1213,13 +1225,13 @@
         <v>38</v>
       </c>
       <c r="B30" t="s">
+        <v>86</v>
+      </c>
+      <c r="C30" t="s">
+        <v>87</v>
+      </c>
+      <c r="D30" t="s">
         <v>88</v>
-      </c>
-      <c r="C30" t="s">
-        <v>89</v>
-      </c>
-      <c r="D30" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="31" spans="1:8">
@@ -1227,13 +1239,13 @@
         <v>38</v>
       </c>
       <c r="B31" t="s">
+        <v>89</v>
+      </c>
+      <c r="C31" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" t="s">
         <v>91</v>
-      </c>
-      <c r="C31" t="s">
-        <v>89</v>
-      </c>
-      <c r="D31" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="32" spans="1:8">
@@ -1241,10 +1253,10 @@
         <v>38</v>
       </c>
       <c r="B32" t="s">
+        <v>92</v>
+      </c>
+      <c r="C32" t="s">
         <v>93</v>
-      </c>
-      <c r="C32" t="s">
-        <v>89</v>
       </c>
       <c r="D32" t="s">
         <v>94</v>
@@ -1258,7 +1270,7 @@
         <v>95</v>
       </c>
       <c r="C33" t="s">
-        <v>89</v>
+        <v>93</v>
       </c>
       <c r="D33" t="s">
         <v>96</v>
@@ -1272,7 +1284,7 @@
         <v>97</v>
       </c>
       <c r="C34" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D34" t="s">
         <v>98</v>
@@ -1286,7 +1298,7 @@
         <v>99</v>
       </c>
       <c r="C35" t="s">
-        <v>56</v>
+        <v>93</v>
       </c>
       <c r="D35" t="s">
         <v>100</v>
@@ -1300,7 +1312,7 @@
         <v>101</v>
       </c>
       <c r="C36" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="D36" t="s">
         <v>102</v>
@@ -1314,7 +1326,7 @@
         <v>103</v>
       </c>
       <c r="C37" t="s">
-        <v>74</v>
+        <v>60</v>
       </c>
       <c r="D37" t="s">
         <v>104</v>
@@ -1328,7 +1340,7 @@
         <v>105</v>
       </c>
       <c r="C38" t="s">
-        <v>89</v>
+        <v>68</v>
       </c>
       <c r="D38" t="s">
         <v>106</v>
@@ -1342,7 +1354,7 @@
         <v>107</v>
       </c>
       <c r="C39" t="s">
-        <v>40</v>
+        <v>78</v>
       </c>
       <c r="D39" t="s">
         <v>108</v>
@@ -1356,7 +1368,7 @@
         <v>109</v>
       </c>
       <c r="C40" t="s">
-        <v>40</v>
+        <v>93</v>
       </c>
       <c r="D40" t="s">
         <v>110</v>
@@ -1398,10 +1410,10 @@
         <v>115</v>
       </c>
       <c r="C43" t="s">
+        <v>40</v>
+      </c>
+      <c r="D43" t="s">
         <v>116</v>
-      </c>
-      <c r="D43" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="44" spans="1:8">
@@ -1409,6 +1421,12 @@
         <v>38</v>
       </c>
       <c r="B44" t="s">
+        <v>117</v>
+      </c>
+      <c r="C44" t="s">
+        <v>40</v>
+      </c>
+      <c r="D44" t="s">
         <v>118</v>
       </c>
     </row>
@@ -1419,8 +1437,11 @@
       <c r="B45" t="s">
         <v>119</v>
       </c>
+      <c r="C45" t="s">
+        <v>120</v>
+      </c>
       <c r="D45" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="46" spans="1:8">
@@ -1428,9 +1449,6 @@
         <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>121</v>
-      </c>
-      <c r="D46" t="s">
         <v>122</v>
       </c>
     </row>
@@ -1443,6 +1461,28 @@
       </c>
       <c r="D47" t="s">
         <v>124</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8">
+      <c r="A48" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" t="s">
+        <v>125</v>
+      </c>
+      <c r="D48" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8">
+      <c r="A49" t="s">
+        <v>38</v>
+      </c>
+      <c r="B49" t="s">
+        <v>127</v>
+      </c>
+      <c r="D49" t="s">
+        <v>128</v>
       </c>
     </row>
   </sheetData>
